--- a/artfynd/A 15219-2024 artfynd.xlsx
+++ b/artfynd/A 15219-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67748559</v>
+        <v>67748558</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1542</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tårkragskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hemistropharia albocrenulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Jacobss. &amp; E. Larss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Filsbäck - Södra delen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398225.3412649983</v>
+        <v>398131</v>
       </c>
       <c r="R2" t="n">
-        <v>6484208.714572173</v>
+        <v>6484260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +749,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -774,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67748558</v>
+        <v>67748559</v>
       </c>
       <c r="B3" t="n">
-        <v>87824</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,40 +795,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1542</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tårkragskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hemistropharia albocrenulata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jacobss. &amp; E. Larss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Filsbäck - Södra delen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398130.7903142108</v>
+        <v>398225</v>
       </c>
       <c r="R3" t="n">
-        <v>6484260.338319216</v>
+        <v>6484209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +852,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,7 +868,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,6 +883,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>71608283</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Filsbäck, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>398246</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6484300</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sävare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-05-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-05-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15219-2024 artfynd.xlsx
+++ b/artfynd/A 15219-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748558</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748559</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,8 +995,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71608283</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>